--- a/data/trans_orig/P6902-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P6902-Clase-trans_orig.xlsx
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W25"/>
+  <dimension ref="A1:W22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que se siente nervioso y estresado en 2007</t>
+          <t>Población según si su trabajo le afecta de manera que se siente nervioso y estresado en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>43573</t>
+          <t>43291</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>56076</t>
+          <t>55686</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>66,95%</t>
+          <t>66,52%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>86,16%</t>
+          <t>85,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>28922</t>
+          <t>29272</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>41174</t>
+          <t>41196</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>62,0%</t>
+          <t>62,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>88,26%</t>
+          <t>88,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>74838</t>
+          <t>76825</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>93283</t>
+          <t>94150</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>66,98%</t>
+          <t>68,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>83,49%</t>
+          <t>84,26%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9007</t>
+          <t>9397</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21510</t>
+          <t>21792</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>33,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5476</t>
+          <t>5454</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17728</t>
+          <t>17378</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>37,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>18450</t>
+          <t>17583</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>36895</t>
+          <t>34908</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>31,24%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17238</t>
+          <t>15952</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29917</t>
+          <t>29639</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>37,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>70,63%</t>
+          <t>69,98%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21918</t>
+          <t>22012</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>34345</t>
+          <t>33895</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>52,67%</t>
+          <t>52,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>82,53%</t>
+          <t>81,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>41778</t>
+          <t>42194</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>60638</t>
+          <t>60656</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>49,75%</t>
+          <t>50,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>72,21%</t>
+          <t>72,24%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>12438</t>
+          <t>12716</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>25117</t>
+          <t>26403</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>59,3%</t>
+          <t>62,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>7271</t>
+          <t>7721</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>19698</t>
+          <t>19604</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>47,33%</t>
+          <t>47,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>23332</t>
+          <t>23314</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>42192</t>
+          <t>41776</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>50,25%</t>
+          <t>49,75%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>41256</t>
+          <t>41427</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>61898</t>
+          <t>62073</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>41,24%</t>
+          <t>41,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>61,88%</t>
+          <t>62,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1126</t>
+          <t>1116</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9239</t>
+          <t>9289</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>56,73%</t>
+          <t>57,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>45338</t>
+          <t>46811</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>67816</t>
+          <t>68257</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>38,98%</t>
+          <t>40,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>58,3%</t>
+          <t>58,68%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>38132</t>
+          <t>37957</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>58774</t>
+          <t>58603</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>38,12%</t>
+          <t>37,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>58,76%</t>
+          <t>58,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7048</t>
+          <t>6998</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15161</t>
+          <t>15171</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>43,27%</t>
+          <t>42,97%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>48500</t>
+          <t>48059</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>70978</t>
+          <t>69505</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>41,7%</t>
+          <t>41,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>61,02%</t>
+          <t>59,76%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>51038</t>
+          <t>50451</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>78117</t>
+          <t>76991</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>38,34%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17744</t>
+          <t>17557</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31850</t>
+          <t>32021</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>63,77%</t>
+          <t>64,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>73938</t>
+          <t>74315</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>105453</t>
+          <t>104726</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>42,05%</t>
+          <t>41,76%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>122712</t>
+          <t>123838</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>149791</t>
+          <t>150378</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>61,1%</t>
+          <t>61,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,59%</t>
+          <t>74,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>18096</t>
+          <t>17925</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>32202</t>
+          <t>32389</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>36,23%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>64,47%</t>
+          <t>64,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>145322</t>
+          <t>146049</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>176837</t>
+          <t>176460</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>57,95%</t>
+          <t>58,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,52%</t>
+          <t>70,37%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8941</t>
+          <t>9711</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23958</t>
+          <t>25309</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>39,54%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12399</t>
+          <t>11837</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>26915</t>
+          <t>27024</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>41,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>25313</t>
+          <t>25646</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>45454</t>
+          <t>46622</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,06%</t>
+          <t>35,96%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>40051</t>
+          <t>38700</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>55068</t>
+          <t>54298</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>62,57%</t>
+          <t>60,46%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>84,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>38708</t>
+          <t>38599</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>53224</t>
+          <t>53786</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>58,99%</t>
+          <t>58,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>81,1%</t>
+          <t>81,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>84178</t>
+          <t>83010</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>104319</t>
+          <t>103986</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>64,94%</t>
+          <t>64,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>80,47%</t>
+          <t>80,22%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2438,107 +2438,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>191</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>205061</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>185412</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>229307</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>43,42%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>39,26%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>48,55%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>111</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>113018</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>97668</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>126680</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>51,34%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>44,37%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>57,55%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>302</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>318079</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>292908</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>345489</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>45,94%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>42,3%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>49,9%</t>
         </is>
       </c>
     </row>
@@ -2551,107 +2551,107 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>259</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>267244</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>242998</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>286893</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>56,58%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>51,45%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>60,74%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>104</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>107103</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>93441</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>122453</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>48,66%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>42,45%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>55,63%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>363</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>374348</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>346938</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>399519</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>54,06%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>50,1%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>57,7%</t>
         </is>
       </c>
     </row>
@@ -2664,462 +2664,119 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>450</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>472305</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>472305</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>472305</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>215</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>220121</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>220121</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>220121</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>665</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>692427</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>692427</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>692427</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>191</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>205061</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>182842</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>226766</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>43,42%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>38,71%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>48,01%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>113018</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>99095</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>129325</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>51,34%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>45,02%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>58,75%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>302</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>318079</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>292085</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>343979</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>45,94%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>42,18%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>49,68%</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n"/>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>259</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>267244</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>245539</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>289463</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>56,58%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>51,99%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>61,29%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>107103</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>90796</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>121026</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>48,66%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>41,25%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>54,98%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>363</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>374348</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>348448</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>400342</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>54,06%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>50,32%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>57,82%</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n"/>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>450</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>472305</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>472305</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>472305</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>220121</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>220121</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>220121</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>665</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>692427</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>692427</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>692427</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
@@ -3129,7 +2786,6 @@
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
-    <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3142,7 +2798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W25"/>
+  <dimension ref="A1:W22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3173,7 +2829,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que se siente nervioso y estresado en 2012</t>
+          <t>Población según si su trabajo le afecta de manera que se siente nervioso y estresado en 2012 (tasa de respuesta: 98,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3024,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>27460</t>
+          <t>26512</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>41670</t>
+          <t>41421</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3039,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>49,51%</t>
+          <t>47,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>75,14%</t>
+          <t>74,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3059,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>29922</t>
+          <t>29973</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>40441</t>
+          <t>40087</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3074,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>68,21%</t>
+          <t>68,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3094,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>60693</t>
+          <t>61749</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>79161</t>
+          <t>79247</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3109,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>61,1%</t>
+          <t>62,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>79,7%</t>
+          <t>79,78%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3137,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13788</t>
+          <t>14037</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27998</t>
+          <t>28946</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3152,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>50,49%</t>
+          <t>52,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3172,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3428</t>
+          <t>3782</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13947</t>
+          <t>13896</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3187,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3207,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>20167</t>
+          <t>20081</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>38635</t>
+          <t>37579</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3222,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>37,83%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3367,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18065</t>
+          <t>18538</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29842</t>
+          <t>30017</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3382,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>49,71%</t>
+          <t>51,01%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>82,11%</t>
+          <t>82,6%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3402,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10259</t>
+          <t>9654</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21323</t>
+          <t>20773</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3417,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>38,55%</t>
+          <t>36,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>80,12%</t>
+          <t>78,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3437,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>31076</t>
+          <t>31428</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>48019</t>
+          <t>48397</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3452,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>49,36%</t>
+          <t>49,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>76,27%</t>
+          <t>76,87%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3480,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6500</t>
+          <t>6325</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>18277</t>
+          <t>17804</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3495,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>50,29%</t>
+          <t>48,99%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3515,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>5291</t>
+          <t>5841</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>16355</t>
+          <t>16960</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3530,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>61,45%</t>
+          <t>63,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3550,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>14937</t>
+          <t>14559</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>31880</t>
+          <t>31528</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3565,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>50,64%</t>
+          <t>50,08%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +3710,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>23197</t>
+          <t>23284</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>40860</t>
+          <t>40570</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +3725,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>52,16%</t>
+          <t>51,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +3745,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9636</t>
+          <t>10338</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22153</t>
+          <t>22627</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +3760,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>65,69%</t>
+          <t>67,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +3780,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>38348</t>
+          <t>38124</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>59739</t>
+          <t>59078</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +3795,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>53,31%</t>
+          <t>52,72%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +3823,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>37482</t>
+          <t>37772</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>55145</t>
+          <t>55058</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +3838,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>47,84%</t>
+          <t>48,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>70,39%</t>
+          <t>70,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +3858,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11569</t>
+          <t>11095</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>24086</t>
+          <t>23384</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +3873,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>71,42%</t>
+          <t>69,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +3893,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>52324</t>
+          <t>52985</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>73715</t>
+          <t>73939</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +3908,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>46,69%</t>
+          <t>47,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>65,78%</t>
+          <t>65,98%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4053,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>38854</t>
+          <t>37720</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>60646</t>
+          <t>60207</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4068,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>52,13%</t>
+          <t>51,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4088,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23915</t>
+          <t>24536</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>40638</t>
+          <t>40706</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4103,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>35,19%</t>
+          <t>36,11%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>59,8%</t>
+          <t>59,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4123,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>68726</t>
+          <t>67245</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>96665</t>
+          <t>95745</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4138,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>37,29%</t>
+          <t>36,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>52,45%</t>
+          <t>51,95%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4166,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>55698</t>
+          <t>56137</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>77490</t>
+          <t>78624</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4181,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>47,87%</t>
+          <t>48,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>66,6%</t>
+          <t>67,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4201,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>27317</t>
+          <t>27249</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>44040</t>
+          <t>43419</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4216,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>40,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>64,81%</t>
+          <t>63,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4236,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>87634</t>
+          <t>88554</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>115573</t>
+          <t>117054</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4251,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>47,55%</t>
+          <t>48,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>62,71%</t>
+          <t>63,51%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4396,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5957</t>
+          <t>5919</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17802</t>
+          <t>17551</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4411,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>46,1%</t>
+          <t>45,45%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4431,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16600</t>
+          <t>16597</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>30561</t>
+          <t>30468</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4795,7 +4451,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>69,99%</t>
+          <t>69,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4466,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>24812</t>
+          <t>25996</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>44096</t>
+          <t>45519</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4481,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>31,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>53,59%</t>
+          <t>55,32%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4509,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20817</t>
+          <t>21068</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>32662</t>
+          <t>32700</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4524,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>53,9%</t>
+          <t>54,55%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,58%</t>
+          <t>84,67%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4544,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13107</t>
+          <t>13200</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>27068</t>
+          <t>27071</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,7 +4559,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>30,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4923,12 +4579,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>38191</t>
+          <t>36768</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>57475</t>
+          <t>56291</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4594,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>46,41%</t>
+          <t>44,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,85%</t>
+          <t>68,41%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +4719,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5073,107 +4729,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>145</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>152372</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>134651</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>170371</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>46,87%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>41,42%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>52,4%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>115</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>124186</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>107731</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>138490</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>57,54%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>49,92%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>64,17%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>260</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>276558</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>251828</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>299706</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>51,13%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>46,55%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>55,41%</t>
         </is>
       </c>
     </row>
@@ -5186,107 +4842,107 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>167</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>172733</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>154734</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>190454</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>53,13%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>47,6%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>58,58%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>83</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>91642</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>77338</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>108097</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>42,46%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>35,83%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>50,08%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>250</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>264375</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>241227</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>289105</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>48,87%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>44,59%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>53,45%</t>
         </is>
       </c>
     </row>
@@ -5299,462 +4955,119 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>312</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>325105</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>325105</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>325105</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>198</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>215828</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>215828</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>215828</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>510</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>540933</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>540933</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>540933</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>152372</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>133156</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>170842</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>46,87%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>40,96%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>52,55%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>124186</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>108010</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>138217</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>57,54%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>50,04%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>64,04%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>260</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>276558</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>252559</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>300396</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>51,13%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>46,69%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>55,53%</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n"/>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>172733</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>154263</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>191949</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>53,13%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>47,45%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>59,04%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>91642</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>77611</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>107818</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>42,46%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>35,96%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>49,96%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>264375</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>240537</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>288374</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>48,87%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>44,47%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>53,31%</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n"/>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>312</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>325105</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>325105</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>325105</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>215828</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>215828</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>215828</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>510</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>540933</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>540933</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>540933</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
@@ -5764,7 +5077,6 @@
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
-    <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5777,7 +5089,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W25"/>
+  <dimension ref="A1:W22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5808,7 +5120,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que se siente nervioso y estresado en 2016</t>
+          <t>Población según si su trabajo le afecta de manera que se siente nervioso y estresado en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +5315,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>28150</t>
+          <t>27968</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>39704</t>
+          <t>40069</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +5330,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>60,01%</t>
+          <t>59,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>84,64%</t>
+          <t>85,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +5350,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>25162</t>
+          <t>25674</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>37784</t>
+          <t>38645</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +5365,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>54,78%</t>
+          <t>55,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>82,26%</t>
+          <t>84,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +5385,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>57087</t>
+          <t>57181</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>74604</t>
+          <t>74880</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +5400,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>61,49%</t>
+          <t>61,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>80,35%</t>
+          <t>80,65%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +5428,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7207</t>
+          <t>6842</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18761</t>
+          <t>18943</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +5443,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>39,99%</t>
+          <t>40,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +5463,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>7289</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20772</t>
+          <t>20260</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +5478,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>45,22%</t>
+          <t>44,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +5498,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>18241</t>
+          <t>17965</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>35758</t>
+          <t>35664</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +5513,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>38,51%</t>
+          <t>38,41%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +5658,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12064</t>
+          <t>12516</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22941</t>
+          <t>23507</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +5673,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>39,9%</t>
+          <t>41,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>75,87%</t>
+          <t>77,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +5693,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17003</t>
+          <t>17093</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26544</t>
+          <t>26405</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +5708,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>57,85%</t>
+          <t>58,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>89,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +5728,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>33116</t>
+          <t>32309</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>47835</t>
+          <t>47284</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +5743,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>55,54%</t>
+          <t>54,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>80,22%</t>
+          <t>79,29%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +5771,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7295</t>
+          <t>6729</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>18172</t>
+          <t>17720</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +5786,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>60,1%</t>
+          <t>58,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +5806,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2850</t>
+          <t>2989</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>12391</t>
+          <t>12301</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +5821,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>42,15%</t>
+          <t>41,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +5841,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>11796</t>
+          <t>12347</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>26515</t>
+          <t>27322</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +5856,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>44,46%</t>
+          <t>45,82%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6001,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15414</t>
+          <t>14729</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>31084</t>
+          <t>31910</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6016,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>46,47%</t>
+          <t>47,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6036,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3201</t>
+          <t>3038</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8685</t>
+          <t>8647</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6051,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6071,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>20886</t>
+          <t>21249</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>38261</t>
+          <t>37975</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6086,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>50,04%</t>
+          <t>49,67%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6114,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>35806</t>
+          <t>34980</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>51476</t>
+          <t>52161</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6129,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>53,53%</t>
+          <t>52,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>76,96%</t>
+          <t>77,98%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6149,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>884</t>
+          <t>922</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6368</t>
+          <t>6531</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6164,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>66,54%</t>
+          <t>68,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6184,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>38198</t>
+          <t>38484</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>55573</t>
+          <t>55210</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6199,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>49,96%</t>
+          <t>50,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>72,68%</t>
+          <t>72,21%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +6344,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>47290</t>
+          <t>47158</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>69771</t>
+          <t>70260</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +6359,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>34,55%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>50,98%</t>
+          <t>51,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +6379,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>39195</t>
+          <t>39351</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>58010</t>
+          <t>57970</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +6394,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>46,62%</t>
+          <t>46,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>69,0%</t>
+          <t>68,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +6414,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>92421</t>
+          <t>92793</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>122246</t>
+          <t>121941</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +6429,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>41,83%</t>
+          <t>42,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>55,33%</t>
+          <t>55,19%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +6457,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>67098</t>
+          <t>66609</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>89579</t>
+          <t>89711</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +6472,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>49,02%</t>
+          <t>48,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>65,45%</t>
+          <t>65,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +6492,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>26067</t>
+          <t>26107</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>44882</t>
+          <t>44726</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +6507,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>31,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>53,38%</t>
+          <t>53,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +6527,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>98700</t>
+          <t>99005</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>128525</t>
+          <t>128153</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +6542,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>44,67%</t>
+          <t>44,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>58,17%</t>
+          <t>58,0%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +6687,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10652</t>
+          <t>11195</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>25191</t>
+          <t>26674</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +6702,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>38,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +6722,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13738</t>
+          <t>13817</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>26872</t>
+          <t>26879</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +6737,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>56,78%</t>
+          <t>56,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +6757,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>28250</t>
+          <t>28375</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>47546</t>
+          <t>49652</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +6772,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,84%</t>
+          <t>42,65%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +6800,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>43904</t>
+          <t>42421</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>58443</t>
+          <t>57900</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +6815,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>63,54%</t>
+          <t>61,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,58%</t>
+          <t>83,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +6835,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>20452</t>
+          <t>20445</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>33586</t>
+          <t>33507</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +6850,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>43,22%</t>
+          <t>43,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>70,97%</t>
+          <t>70,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +6870,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>68873</t>
+          <t>66767</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>88169</t>
+          <t>88044</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +6885,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>59,16%</t>
+          <t>57,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>75,73%</t>
+          <t>75,63%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7010,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7708,107 +7020,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>137</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>151995</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>132941</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>171739</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>43,43%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>37,98%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>49,07%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>125</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>131034</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>116377</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>144767</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>60,58%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>53,8%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>66,93%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>262</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>283029</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>258995</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>307871</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>49,98%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>45,73%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>54,37%</t>
         </is>
       </c>
     </row>
@@ -7821,107 +7133,107 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>185</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>198006</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>178262</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>217060</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>56,57%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>50,93%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>62,02%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>82</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>85264</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>71531</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>99921</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>39,42%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>33,07%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>46,2%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>267</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>283270</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>258428</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>307304</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>50,02%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>45,63%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>54,27%</t>
         </is>
       </c>
     </row>
@@ -7934,462 +7246,119 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>322</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>350001</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>350001</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>350001</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>207</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>216298</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>216298</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>216298</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>529</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>566299</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>566299</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>566299</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>151995</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>132290</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>170699</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>43,43%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>37,8%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>48,77%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>131034</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>115947</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>145027</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>60,58%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>53,61%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>67,05%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>262</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>283029</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>256966</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>307060</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>49,98%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>45,38%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>54,22%</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n"/>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>185</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>198006</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>179302</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>217711</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>56,57%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>51,23%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>62,2%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>85264</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>71271</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>100351</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>39,42%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>32,95%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>46,39%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>267</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>283270</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>259239</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>309333</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>50,02%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>45,78%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>54,62%</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n"/>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>322</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>350001</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>350001</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>350001</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>216298</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>216298</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>216298</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>529</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>566299</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>566299</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>566299</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
@@ -8399,7 +7368,6 @@
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
-    <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8412,7 +7380,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W25"/>
+  <dimension ref="A1:W22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8443,7 +7411,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que se siente nervioso y estresado en 2023</t>
+          <t>Población según si su trabajo le afecta de manera que se siente nervioso y estresado en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +7606,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>38166</t>
+          <t>37828</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>44915</t>
+          <t>44894</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +7621,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>83,3%</t>
+          <t>82,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +7641,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>44177</t>
+          <t>44407</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>53586</t>
+          <t>53311</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +7656,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>74,51%</t>
+          <t>74,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>89,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +7676,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>85341</t>
+          <t>85415</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>97090</t>
+          <t>97430</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +7691,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>81,19%</t>
+          <t>81,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,7%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +7719,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>901</t>
+          <t>922</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7650</t>
+          <t>7988</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +7734,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +7754,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5704</t>
+          <t>5979</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15113</t>
+          <t>14883</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +7769,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +7789,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8016</t>
+          <t>7676</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>19765</t>
+          <t>19691</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +7804,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,73%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +7949,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>35821</t>
+          <t>36447</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>47669</t>
+          <t>47769</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +7964,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>70,54%</t>
+          <t>71,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +7984,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29463</t>
+          <t>28925</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>37991</t>
+          <t>37650</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +7999,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>69,89%</t>
+          <t>68,61%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>89,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +8019,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>69731</t>
+          <t>68582</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>83934</t>
+          <t>84303</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +8034,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>75,03%</t>
+          <t>73,79%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>90,71%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +8062,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3110</t>
+          <t>3010</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14958</t>
+          <t>14332</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +8077,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +8097,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4167</t>
+          <t>4508</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>12695</t>
+          <t>13233</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +8112,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +8132,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>9003</t>
+          <t>8634</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>23206</t>
+          <t>24355</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +8147,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>26,21%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +8292,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19300</t>
+          <t>19621</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>35578</t>
+          <t>35893</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +8307,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>33,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>60,79%</t>
+          <t>61,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +8327,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5972</t>
+          <t>5994</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12856</t>
+          <t>12970</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +8342,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>33,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>72,07%</t>
+          <t>72,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +8362,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>27833</t>
+          <t>28199</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>45034</t>
+          <t>44570</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +8377,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>36,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>58,97%</t>
+          <t>58,37%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +8405,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22945</t>
+          <t>22630</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>39223</t>
+          <t>38902</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +8420,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>39,21%</t>
+          <t>38,67%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>67,02%</t>
+          <t>66,47%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +8440,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4983</t>
+          <t>4869</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11867</t>
+          <t>11845</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +8455,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>66,53%</t>
+          <t>66,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +8475,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>31328</t>
+          <t>31792</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>48529</t>
+          <t>48163</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +8490,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>41,03%</t>
+          <t>41,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>63,55%</t>
+          <t>63,07%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +8635,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>60846</t>
+          <t>59779</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>85844</t>
+          <t>85408</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +8650,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>45,67%</t>
+          <t>44,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>64,44%</t>
+          <t>64,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +8670,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>60348</t>
+          <t>60977</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>76703</t>
+          <t>77593</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +8685,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>57,06%</t>
+          <t>57,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>72,53%</t>
+          <t>73,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +8705,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>126523</t>
+          <t>127761</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>156471</t>
+          <t>158655</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +8720,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>52,94%</t>
+          <t>53,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>65,48%</t>
+          <t>66,39%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +8748,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>47374</t>
+          <t>47810</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>72372</t>
+          <t>73439</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +8763,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>54,33%</t>
+          <t>55,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +8783,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>29055</t>
+          <t>28165</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>45410</t>
+          <t>44781</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +8798,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>42,94%</t>
+          <t>42,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +8818,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>82505</t>
+          <t>80321</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>112453</t>
+          <t>111215</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +8833,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>34,52%</t>
+          <t>33,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>47,06%</t>
+          <t>46,54%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +8978,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>16717</t>
+          <t>16295</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>31843</t>
+          <t>31907</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +8993,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>31,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>62,23%</t>
+          <t>62,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +9013,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>22710</t>
+          <t>22604</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>72608</t>
+          <t>73470</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +9028,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>57,06%</t>
+          <t>57,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +9048,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>39668</t>
+          <t>39214</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>97002</t>
+          <t>97244</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +9063,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>54,37%</t>
+          <t>54,5%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +9091,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19327</t>
+          <t>19263</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>34453</t>
+          <t>34875</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +9106,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>37,77%</t>
+          <t>37,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>67,33%</t>
+          <t>68,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +9126,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>54639</t>
+          <t>53777</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>104537</t>
+          <t>104643</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +9141,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>42,94%</t>
+          <t>42,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,15%</t>
+          <t>82,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +9161,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>81414</t>
+          <t>81172</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>138748</t>
+          <t>139202</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +9176,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>45,63%</t>
+          <t>45,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>77,77%</t>
+          <t>78,02%</t>
         </is>
       </c>
     </row>
@@ -10333,7 +9301,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10343,107 +9311,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>202</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>209966</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>190398</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>227815</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>61,84%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>56,08%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>67,1%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>311</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>213006</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>155661</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>241889</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>60,46%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>44,19%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>68,66%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>513</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>422972</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>352219</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>454492</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>61,14%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>50,91%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>65,7%</t>
         </is>
       </c>
     </row>
@@ -10456,107 +9424,107 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>136</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>129539</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>111690</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>149107</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>38,16%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>43,92%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>160</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>139286</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>110403</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>196631</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>39,54%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>31,34%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>55,81%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>296</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>268825</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>237305</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>339578</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>38,86%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>49,09%</t>
         </is>
       </c>
     </row>
@@ -10569,462 +9537,119 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>338</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>339505</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>339505</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>339505</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>471</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>352292</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>352292</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>352292</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>809</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>691797</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>691797</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>691797</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>209966</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>191466</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>227618</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>61,84%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>56,4%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>67,04%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>311</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>213006</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>154677</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>241350</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>60,46%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>43,91%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>68,51%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>513</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>422972</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>355858</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>456106</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>61,14%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>51,44%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>65,93%</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n"/>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>136</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>129539</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>111887</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>148039</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>38,16%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>32,96%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>43,6%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>139286</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>110942</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>197615</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>39,54%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>31,49%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>56,09%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>296</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>268825</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>235691</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>335939</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>38,86%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>34,07%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>48,56%</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n"/>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>338</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>339505</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>339505</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>339505</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>471</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>352292</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>352292</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>352292</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>809</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>691797</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>691797</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>691797</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
@@ -11034,7 +9659,6 @@
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
-    <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
